--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_o_ocup_a_2021.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_o_ocup_a_2021.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:21</t>
+    <t xml:space="preserve">2026-09-24 01:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -810,7 +810,7 @@
         <v>-0.75</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="21">
@@ -824,7 +824,7 @@
         <v>-0.22</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="22">
@@ -838,7 +838,7 @@
         <v>-0.64</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="23">
@@ -852,7 +852,7 @@
         <v>-0.41</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="24">

--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_o_ocup_a_2021.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_o_ocup_a_2021.xlsx
@@ -117,7 +117,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:11</t>
+    <t xml:space="preserve">2026-10-01 23:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_o_ocup_a_2021.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_o_ocup_a_2021.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:05</t>
+    <t xml:space="preserve">2026-10-05 19:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
